--- a/astro-site/public/dl/pack-appcc/10-control-agua-potable.xlsx
+++ b/astro-site/public/dl/pack-appcc/10-control-agua-potable.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Control Agua" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Agua" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Control Agua'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -115,27 +117,27 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -495,15 +497,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -511,6 +514,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -518,9 +522,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -556,13 +558,19 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -570,7 +578,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -579,18 +596,18 @@
   <sheetPr>
     <tabColor rgb="0003A9F4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="14"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="15"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
-    <col customWidth="1" max="7" min="7" width="20"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -607,6 +624,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -824,6 +842,7 @@
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="7" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -843,11 +862,19 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19" type="list">
+    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Normal,Turbio,Olor extraño,Color anormal"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/10-control-agua-potable.xlsx
+++ b/astro-site/public/dl/pack-appcc/10-control-agua-potable.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Agua" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Control Agua'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Control Agua'!$A$1:$G$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +74,31 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -92,8 +117,18 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,11 +150,25 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,10 +182,77 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -499,16 +615,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Registro de Control de Agua Potable</t>
         </is>
@@ -516,7 +632,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -524,61 +640,145 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Si tu agua viene de la red municipal: registro simplificado</t>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>▸ Marca arriba de qué fuente viene tu agua: red municipal, pozo propio o depósito. De eso depende la frecuencia.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Si tienes pozo o depósito propio: análisis obligatorios</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>▸ Anota el cloro residual libre en mg/L y elige el aspecto / olor en el desplegable. El Estado se calcula solo y se pinta.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Registra niveles de cloro residual (0.2-1.0 mg/L)</t>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>▸ Si tienes pozo o depósito propio, además son obligatorios los análisis por laboratorio: marca «Análisis externo = S» y guarda el boletín con esta hoja.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>▸ Guarda los boletines de análisis de la empresa de agua</t>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>▸ Si el agua viene de la red municipal, guarda también los boletines que publica tu gestor de abastecimiento.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>▸ Obligatorio según RD 140/2003</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Qué significa cada Estado</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>▸ OK — cloro entre 0,2 y 1,0 mg/L y aspecto Normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>▸ INCOMPLETO (ámbar) — has medido el cloro pero falta el aspecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>▸ FALTA CLORO (ámbar) — el aspecto es normal pero no hay medida de cloro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸ REVISAR (rojo) — el aspecto es anormal (turbio, olor extraño, color) o el cloro está fuera de rango. El aspecto anormal manda aunque no hayas llegado a medir el cloro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Frecuencia recomendada</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>▸ Con depósito propio o pozo: control diario de cloro residual en un punto de la instalación (por eso la hoja trae 31 filas: un mes completo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>▸ Con agua de red y sin depósito: control semanal, rotando los puntos de muestreo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>▸ Tras cualquier obra, limpieza de depósito o corte de suministro: medir antes de volver a usar el agua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Marco normativo y archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>▸ RD 3/2023, de 10 de enero, por el que se establecen los criterios técnico-sanitarios de la calidad del agua de consumo (sustituye íntegramente al reglamento anterior).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+    <row r="30"/>
+    <row r="31">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -598,20 +798,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Registro de Control de Agua Potable</t>
         </is>
@@ -620,253 +820,519 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fuente de suministro: ☐ Red municipal   ☐ Pozo propio   ☐ Depósito</t>
+          <t>Fuente de suministro: ☐ Red municipal   ☐ Pozo propio   ☐ Depósito        Responsable: ____________________</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Punto de Muestreo</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Cloro Residual (mg/L)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Aspecto / Olor</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Punto de muestreo</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Cloro residual (mg/L)</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Aspecto / olor</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Análisis Externo (S/N)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Análisis externo (S/N)</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7">
-        <f>IF(C5="","",IF(AND(C5&gt;=0.2,C5&lt;=1.0,D5="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7">
-        <f>IF(C6="","",IF(AND(C6&gt;=0.2,C6&lt;=1.0,D6="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7">
-        <f>IF(C7="","",IF(AND(C7&gt;=0.2,C7&lt;=1.0,D7="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7">
-        <f>IF(C8="","",IF(AND(C8&gt;=0.2,C8&lt;=1.0,D8="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7">
-        <f>IF(C9="","",IF(AND(C9&gt;=0.2,C9&lt;=1.0,D9="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7">
-        <f>IF(C10="","",IF(AND(C10&gt;=0.2,C10&lt;=1.0,D10="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7">
-        <f>IF(C11="","",IF(AND(C11&gt;=0.2,C11&lt;=1.0,D11="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7">
-        <f>IF(C12="","",IF(AND(C12&gt;=0.2,C12&lt;=1.0,D12="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7">
-        <f>IF(C13="","",IF(AND(C13&gt;=0.2,C13&lt;=1.0,D13="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7">
-        <f>IF(C14="","",IF(AND(C14&gt;=0.2,C14&lt;=1.0,D14="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7">
-        <f>IF(C15="","",IF(AND(C15&gt;=0.2,C15&lt;=1.0,D15="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7">
-        <f>IF(C16="","",IF(AND(C16&gt;=0.2,C16&lt;=1.0,D16="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7">
-        <f>IF(C17="","",IF(AND(C17&gt;=0.2,C17&lt;=1.0,D17="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7">
-        <f>IF(C18="","",IF(AND(C18&gt;=0.2,C18&lt;=1.0,D18="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7">
-        <f>IF(C19="","",IF(AND(C19&gt;=0.2,C19&lt;=1.0,D19="Normal"),"OK","REVISAR"))</f>
-        <v/>
-      </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Cloro residual aceptable: 0.2 - 1.0 mg/L (RD 140/2003).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Grifo cocina</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="str">
+        <f>IF(AND($C5="",$D5=""),"",IF(AND($D5&lt;&gt;"",$D5&lt;&gt;"Normal"),"REVISAR",IF($C5="","FALTA CLORO",IF($D5="","INCOMPLETO",IF(AND($C5&gt;=0.2,$C5&lt;=1),"OK","REVISAR")))))</f>
+        <v>OK</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Grifo office</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="str">
+        <f>IF(AND($C6="",$D6=""),"",IF(AND($D6&lt;&gt;"",$D6&lt;&gt;"Normal"),"REVISAR",IF($C6="","FALTA CLORO",IF($D6="","INCOMPLETO",IF(AND($C6&gt;=0.2,$C6&lt;=1),"OK","REVISAR")))))</f>
+        <v>REVISAR</v>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Cloro por debajo de 0,2 mg/L: avisado el gestor de la red (ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Grifo cocina</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Turbio</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="str">
+        <f>IF(AND($C7="",$D7=""),"",IF(AND($D7&lt;&gt;"",$D7&lt;&gt;"Normal"),"REVISAR",IF($C7="","FALTA CLORO",IF($D7="","INCOMPLETO",IF(AND($C7&gt;=0.2,$C7&lt;=1),"OK","REVISAR")))))</f>
+        <v>REVISAR</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Agua turbia: cerrado el punto y solicitado análisis externo · incidencia INC-003 (ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="17">
+        <f>IF(AND($C8="",$D8=""),"",IF(AND($D8&lt;&gt;"",$D8&lt;&gt;"Normal"),"REVISAR",IF($C8="","FALTA CLORO",IF($D8="","INCOMPLETO",IF(AND($C8&gt;=0.2,$C8&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="17">
+        <f>IF(AND($C9="",$D9=""),"",IF(AND($D9&lt;&gt;"",$D9&lt;&gt;"Normal"),"REVISAR",IF($C9="","FALTA CLORO",IF($D9="","INCOMPLETO",IF(AND($C9&gt;=0.2,$C9&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="17">
+        <f>IF(AND($C10="",$D10=""),"",IF(AND($D10&lt;&gt;"",$D10&lt;&gt;"Normal"),"REVISAR",IF($C10="","FALTA CLORO",IF($D10="","INCOMPLETO",IF(AND($C10&gt;=0.2,$C10&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="17">
+        <f>IF(AND($C11="",$D11=""),"",IF(AND($D11&lt;&gt;"",$D11&lt;&gt;"Normal"),"REVISAR",IF($C11="","FALTA CLORO",IF($D11="","INCOMPLETO",IF(AND($C11&gt;=0.2,$C11&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="17">
+        <f>IF(AND($C12="",$D12=""),"",IF(AND($D12&lt;&gt;"",$D12&lt;&gt;"Normal"),"REVISAR",IF($C12="","FALTA CLORO",IF($D12="","INCOMPLETO",IF(AND($C12&gt;=0.2,$C12&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="17">
+        <f>IF(AND($C13="",$D13=""),"",IF(AND($D13&lt;&gt;"",$D13&lt;&gt;"Normal"),"REVISAR",IF($C13="","FALTA CLORO",IF($D13="","INCOMPLETO",IF(AND($C13&gt;=0.2,$C13&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="15" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="17">
+        <f>IF(AND($C14="",$D14=""),"",IF(AND($D14&lt;&gt;"",$D14&lt;&gt;"Normal"),"REVISAR",IF($C14="","FALTA CLORO",IF($D14="","INCOMPLETO",IF(AND($C14&gt;=0.2,$C14&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="17">
+        <f>IF(AND($C15="",$D15=""),"",IF(AND($D15&lt;&gt;"",$D15&lt;&gt;"Normal"),"REVISAR",IF($C15="","FALTA CLORO",IF($D15="","INCOMPLETO",IF(AND($C15&gt;=0.2,$C15&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="17">
+        <f>IF(AND($C16="",$D16=""),"",IF(AND($D16&lt;&gt;"",$D16&lt;&gt;"Normal"),"REVISAR",IF($C16="","FALTA CLORO",IF($D16="","INCOMPLETO",IF(AND($C16&gt;=0.2,$C16&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="17">
+        <f>IF(AND($C17="",$D17=""),"",IF(AND($D17&lt;&gt;"",$D17&lt;&gt;"Normal"),"REVISAR",IF($C17="","FALTA CLORO",IF($D17="","INCOMPLETO",IF(AND($C17&gt;=0.2,$C17&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="17">
+        <f>IF(AND($C18="",$D18=""),"",IF(AND($D18&lt;&gt;"",$D18&lt;&gt;"Normal"),"REVISAR",IF($C18="","FALTA CLORO",IF($D18="","INCOMPLETO",IF(AND($C18&gt;=0.2,$C18&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="17">
+        <f>IF(AND($C19="",$D19=""),"",IF(AND($D19&lt;&gt;"",$D19&lt;&gt;"Normal"),"REVISAR",IF($C19="","FALTA CLORO",IF($D19="","INCOMPLETO",IF(AND($C19&gt;=0.2,$C19&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="17">
+        <f>IF(AND($C20="",$D20=""),"",IF(AND($D20&lt;&gt;"",$D20&lt;&gt;"Normal"),"REVISAR",IF($C20="","FALTA CLORO",IF($D20="","INCOMPLETO",IF(AND($C20&gt;=0.2,$C20&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="17">
+        <f>IF(AND($C21="",$D21=""),"",IF(AND($D21&lt;&gt;"",$D21&lt;&gt;"Normal"),"REVISAR",IF($C21="","FALTA CLORO",IF($D21="","INCOMPLETO",IF(AND($C21&gt;=0.2,$C21&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="17">
+        <f>IF(AND($C22="",$D22=""),"",IF(AND($D22&lt;&gt;"",$D22&lt;&gt;"Normal"),"REVISAR",IF($C22="","FALTA CLORO",IF($D22="","INCOMPLETO",IF(AND($C22&gt;=0.2,$C22&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="17">
+        <f>IF(AND($C23="",$D23=""),"",IF(AND($D23&lt;&gt;"",$D23&lt;&gt;"Normal"),"REVISAR",IF($C23="","FALTA CLORO",IF($D23="","INCOMPLETO",IF(AND($C23&gt;=0.2,$C23&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="17">
+        <f>IF(AND($C24="",$D24=""),"",IF(AND($D24&lt;&gt;"",$D24&lt;&gt;"Normal"),"REVISAR",IF($C24="","FALTA CLORO",IF($D24="","INCOMPLETO",IF(AND($C24&gt;=0.2,$C24&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="17">
+        <f>IF(AND($C25="",$D25=""),"",IF(AND($D25&lt;&gt;"",$D25&lt;&gt;"Normal"),"REVISAR",IF($C25="","FALTA CLORO",IF($D25="","INCOMPLETO",IF(AND($C25&gt;=0.2,$C25&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="17">
+        <f>IF(AND($C26="",$D26=""),"",IF(AND($D26&lt;&gt;"",$D26&lt;&gt;"Normal"),"REVISAR",IF($C26="","FALTA CLORO",IF($D26="","INCOMPLETO",IF(AND($C26&gt;=0.2,$C26&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="17">
+        <f>IF(AND($C27="",$D27=""),"",IF(AND($D27&lt;&gt;"",$D27&lt;&gt;"Normal"),"REVISAR",IF($C27="","FALTA CLORO",IF($D27="","INCOMPLETO",IF(AND($C27&gt;=0.2,$C27&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="17">
+        <f>IF(AND($C28="",$D28=""),"",IF(AND($D28&lt;&gt;"",$D28&lt;&gt;"Normal"),"REVISAR",IF($C28="","FALTA CLORO",IF($D28="","INCOMPLETO",IF(AND($C28&gt;=0.2,$C28&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="17">
+        <f>IF(AND($C29="",$D29=""),"",IF(AND($D29&lt;&gt;"",$D29&lt;&gt;"Normal"),"REVISAR",IF($C29="","FALTA CLORO",IF($D29="","INCOMPLETO",IF(AND($C29&gt;=0.2,$C29&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="15" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="14" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="17">
+        <f>IF(AND($C30="",$D30=""),"",IF(AND($D30&lt;&gt;"",$D30&lt;&gt;"Normal"),"REVISAR",IF($C30="","FALTA CLORO",IF($D30="","INCOMPLETO",IF(AND($C30&gt;=0.2,$C30&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="17">
+        <f>IF(AND($C31="",$D31=""),"",IF(AND($D31&lt;&gt;"",$D31&lt;&gt;"Normal"),"REVISAR",IF($C31="","FALTA CLORO",IF($D31="","INCOMPLETO",IF(AND($C31&gt;=0.2,$C31&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="17">
+        <f>IF(AND($C32="",$D32=""),"",IF(AND($D32&lt;&gt;"",$D32&lt;&gt;"Normal"),"REVISAR",IF($C32="","FALTA CLORO",IF($D32="","INCOMPLETO",IF(AND($C32&gt;=0.2,$C32&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="17">
+        <f>IF(AND($C33="",$D33=""),"",IF(AND($D33&lt;&gt;"",$D33&lt;&gt;"Normal"),"REVISAR",IF($C33="","FALTA CLORO",IF($D33="","INCOMPLETO",IF(AND($C33&gt;=0.2,$C33&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="14" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="17">
+        <f>IF(AND($C34="",$D34=""),"",IF(AND($D34&lt;&gt;"",$D34&lt;&gt;"Normal"),"REVISAR",IF($C34="","FALTA CLORO",IF($D34="","INCOMPLETO",IF(AND($C34&gt;=0.2,$C34&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="17">
+        <f>IF(AND($C35="",$D35=""),"",IF(AND($D35&lt;&gt;"",$D35&lt;&gt;"Normal"),"REVISAR",IF($C35="","FALTA CLORO",IF($D35="","INCOMPLETO",IF(AND($C35&gt;=0.2,$C35&lt;=1),"OK","REVISAR")))))</f>
+      </c>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="15" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37" ht="12.2" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Cloro residual libre aceptable en el punto de consumo: 0,2 - 1,0 mg/L (RD 3/2023, de 10 de enero, sobre criterios técnico-sanitarios de la calidad del agua de consumo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="12.2" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>INCOMPLETO = falta el aspecto. FALTA CLORO = falta la medida de cloro. REVISAR = hay una desviación real. La hoja nunca da OK con un dato sin rellenar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24.5" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="12.2" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="41"/>
+    <row r="42"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <conditionalFormatting sqref="E5:E35">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>OR(E5="ALERTA",E5="RECHAZAR",E5="CAMBIAR",E5="REVISAR",E5="✗",E5="CADUCADO",E5="EXCESO")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>OR(E5="VIGILAR",E5="⚠",E5="INCOMPLETO",E5="CADUCA PRONTO",E5="RENOVAR",E5="FALTA CLORO",E5="FALTA TEST",E5="FALTA CLORO")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>OR(E5="OK",E5="✓",E5="Cumple",E5="VIGENTE",E5="Completo",E5="APTO")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="D5:D35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Aspecto / olor" error="Elige una opción de la lista. El Estado la compara con «Normal», así que un texto libre no se reconoce." type="list" errorStyle="stop">
       <formula1>"Normal,Turbio,Olor extraño,Color anormal"</formula1>
     </dataValidation>
+    <dataValidation sqref="F5:F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Análisis externo" error="Escribe S o N." type="list" errorStyle="stop">
+      <formula1>"S,N"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Cloro residual" error="Introduce el cloro residual libre en mg/L, entre 0 y 5." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
